--- a/TOP_PROFIT_3_15_1210.xlsx
+++ b/TOP_PROFIT_3_15_1210.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Топ по прибыли 3–15 млн" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Топ по прибыли 3–15 млн'!$A$3:$U$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Топ по прибыли 3–15 млн'!$A$3:$U$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -512,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Топ лотов по прибыли: НМЦК 3–15 млн ₽, подача с 14.10.2026, без жёстких условий — ВНУТРЕННЯЯ</t>
+          <t>Топ лотов по прибыли: НМЦК 3–15 млн ₽, подача с 16.10.2026, без жёстких условий — ВНУТРЕННЯЯ</t>
         </is>
       </c>
     </row>
@@ -828,12 +828,12 @@
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>18 позиций; НМЦК в 2,8 раза выше каталога Тракт — проверить ТЗ (ткани, ГОСТ)</t>
+          <t>18 позиций; цен за ед. в ЕИС нет — маржа = НМЦК против нашей себестоимости по каталогу Тракт; НМЦК в 2,8 раза выше каталога — проверить ТЗ (ткани, ГОСТ, логотипы)</t>
         </is>
       </c>
       <c r="U5" s="8" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>низкая</t>
         </is>
       </c>
     </row>
@@ -929,766 +929,224 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="n">
+      <c r="A7" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>Соль</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>0118300007926000015</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Форменная одежда</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>0358200022926000030</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>Администрация Лабинского ГП</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>Краснодарский край</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>ГКУ РО «Ростовская обл. поисково-спасательная служба»</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Ростовская обл.</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>44-ФЗ, аукцион</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
-        <is>
-          <t>15.10</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="n">
-        <v>4860000</v>
-      </c>
-      <c r="J7" s="16" t="n">
-        <v>2700000</v>
-      </c>
-      <c r="K7" s="17" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="L7" s="16" t="n">
-        <v>1727500</v>
-      </c>
-      <c r="M7" s="17" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="N7" s="16" t="n">
-        <v>1112807</v>
-      </c>
-      <c r="O7" s="17" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="P7" s="13" t="inlineStr">
-        <is>
-          <t>1% (48 600 ₽)</t>
-        </is>
-      </c>
-      <c r="Q7" s="13" t="inlineStr">
-        <is>
-          <t>см. извещение</t>
-        </is>
-      </c>
-      <c r="R7" s="13" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>19.10 09:00</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>6224421</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>3716512</v>
+      </c>
+      <c r="K7" s="12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="L7" s="11" t="n"/>
+      <c r="M7" s="12" t="n"/>
+      <c r="N7" s="11" t="n">
+        <v>995417</v>
+      </c>
+      <c r="O7" s="12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="P7" s="8" t="inlineStr">
+        <is>
+          <t>1% (62 244 ₽)</t>
+        </is>
+      </c>
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="R7" s="8" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="S7" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T7" s="13" t="inlineStr">
-        <is>
-          <t>8 100 ₽/т — ниже порога 9 000 ₽/т; биг-бэг 1 т</t>
-        </is>
-      </c>
-      <c r="U7" s="13" t="inlineStr">
-        <is>
-          <t>высокая</t>
+      <c r="S7" s="8" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>Пошив с символикой ПСС РО (шевроны, кокетки); только РФ; комбинезоны посчитаны как комплекты</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>средняя</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Форменная одежда</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>0358200022926000030</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Соль</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>0131300000626001316</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>ГКУ РО «Ростовская обл. поисково-спасательная служба»</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>Ростовская обл.</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>МБУ «Комбинат благоустройства Ленинского р-на», Воронеж</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>Воронежская обл.</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>44-ФЗ, аукцион</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>19.10 09:00</t>
-        </is>
-      </c>
-      <c r="I8" s="11" t="n">
-        <v>6224421</v>
-      </c>
-      <c r="J8" s="11" t="n">
-        <v>3716512</v>
-      </c>
-      <c r="K8" s="12" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="L8" s="11" t="n"/>
-      <c r="M8" s="12" t="n"/>
-      <c r="N8" s="11" t="n">
-        <v>995417</v>
-      </c>
-      <c r="O8" s="12" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="P8" s="8" t="inlineStr">
-        <is>
-          <t>1% (62 244 ₽)</t>
-        </is>
-      </c>
-      <c r="Q8" s="8" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>16.10 09:00</t>
+        </is>
+      </c>
+      <c r="I8" s="16" t="n">
+        <v>3296150</v>
+      </c>
+      <c r="J8" s="16" t="n">
+        <v>2074500</v>
+      </c>
+      <c r="K8" s="17" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="L8" s="16" t="n">
+        <v>958016</v>
+      </c>
+      <c r="M8" s="17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N8" s="16" t="n">
+        <v>541119</v>
+      </c>
+      <c r="O8" s="17" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P8" s="13" t="inlineStr">
+        <is>
+          <t>1% (32 962 ₽)</t>
+        </is>
+      </c>
+      <c r="Q8" s="13" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="R8" s="8" t="inlineStr">
+      <c r="R8" s="13" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="S8" s="8" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>Пошив с символикой ПСС РО (шевроны, кокетки); только РФ; комбинезоны посчитаны как комплекты</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>средняя</t>
+      <c r="S8" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T8" s="13" t="inlineStr">
+        <is>
+          <t>7 150 ₽/т — ниже порога 9 000 ₽/т; NaCl ≥96,5%, помол №3</t>
+        </is>
+      </c>
+      <c r="U8" s="13" t="inlineStr">
+        <is>
+          <t>высокая</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>Соль</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>0164300016526000497</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>открыть</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>МБУ «Дирекция благоустройства», Тамбов</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>Тамбовская обл.</t>
-        </is>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
-        <is>
-          <t>44-ФЗ, аукцион</t>
-        </is>
-      </c>
-      <c r="H9" s="13" t="inlineStr">
-        <is>
-          <t>14.10 08:00</t>
-        </is>
-      </c>
-      <c r="I9" s="16" t="n">
-        <v>3910000</v>
-      </c>
-      <c r="J9" s="16" t="n">
-        <v>2070000</v>
-      </c>
-      <c r="K9" s="17" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="L9" s="16" t="n">
-        <v>1479565</v>
-      </c>
-      <c r="M9" s="17" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="N9" s="16" t="n">
-        <v>985029</v>
-      </c>
-      <c r="O9" s="17" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="P9" s="13" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="Q9" s="13" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="R9" s="13" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="S9" s="13" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="T9" s="13" t="inlineStr">
-        <is>
-          <t>8 500 ₽/т — ниже порога 9 000 ₽/т; подача завтра утром</t>
-        </is>
-      </c>
-      <c r="U9" s="13" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Форменная одежда</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>32616443256</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>открыть</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>ГБУ РС(Я) «ГПС РС(Я)»</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>Якутия</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>223-ФЗ</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>15.10 05:00</t>
-        </is>
-      </c>
-      <c r="I10" s="11" t="n">
-        <v>4999002</v>
-      </c>
-      <c r="J10" s="11" t="n">
-        <v>2866350</v>
-      </c>
-      <c r="K10" s="12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L10" s="11" t="n"/>
-      <c r="M10" s="12" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="N10" s="11" t="n">
-        <v>934695</v>
-      </c>
-      <c r="O10" s="12" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="P10" s="8" t="inlineStr">
-        <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="Q10" s="8" t="inlineStr">
-        <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="R10" s="8" t="inlineStr">
-        <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="S10" s="8" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>Зимние комплекты по 9 659 ₽ (Тракт). Если в ТЗ особый пояс −40…−45 °C — лот убыточный. Проверить ТЗ!</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Сигнализация (СС)</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>0335100008526000096</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>открыть</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>ФКУЗ Санаторий «Тройка» ФСИН</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>Калининградская обл.</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>44-ФЗ, аукцион</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>14.10 10:00</t>
-        </is>
-      </c>
-      <c r="I11" s="11" t="n">
-        <v>3927985</v>
-      </c>
-      <c r="J11" s="11" t="n">
-        <v>2603286</v>
-      </c>
-      <c r="K11" s="12" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="L11" s="11" t="n">
-        <v>1026535</v>
-      </c>
-      <c r="M11" s="12" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="N11" s="11" t="n">
-        <v>662206</v>
-      </c>
-      <c r="O11" s="12" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="P11" s="8" t="inlineStr">
-        <is>
-          <t>1% (39 280 ₽)</t>
-        </is>
-      </c>
-      <c r="Q11" s="8" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="R11" s="8" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="S11" s="8" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>Болид, 65 позиций, только поставка; реестровые записи (ПП 1875); подача завтра</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Спецодежда (коммерч.)</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>ГП622514</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>открыть</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>АО «Арго»</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>Коммерческая, ЭТП ГПБ</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>15.10 17:00</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="J12" s="11" t="n">
-        <v>2720000</v>
-      </c>
-      <c r="K12" s="12" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="L12" s="11" t="n"/>
-      <c r="M12" s="12" t="n"/>
-      <c r="N12" s="11" t="n">
-        <v>551989</v>
-      </c>
-      <c r="O12" s="12" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="P12" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q12" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R12" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S12" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>Спецификация закрыта — оценка по аналогам; цены часто сравнивают без НДС</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>Соль</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>0131300000626001316</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>открыть</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>МБУ «Комбинат благоустройства Ленинского р-на», Воронеж</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>Воронежская обл.</t>
-        </is>
-      </c>
-      <c r="G13" s="13" t="inlineStr">
-        <is>
-          <t>44-ФЗ, аукцион</t>
-        </is>
-      </c>
-      <c r="H13" s="13" t="inlineStr">
-        <is>
-          <t>16.10 09:00</t>
-        </is>
-      </c>
-      <c r="I13" s="16" t="n">
-        <v>3296150</v>
-      </c>
-      <c r="J13" s="16" t="n">
-        <v>2074500</v>
-      </c>
-      <c r="K13" s="17" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="L13" s="16" t="n">
-        <v>958016</v>
-      </c>
-      <c r="M13" s="17" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="N13" s="16" t="n">
-        <v>541119</v>
-      </c>
-      <c r="O13" s="17" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="P13" s="13" t="inlineStr">
-        <is>
-          <t>1% (32 962 ₽)</t>
-        </is>
-      </c>
-      <c r="Q13" s="13" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="R13" s="13" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="S13" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T13" s="13" t="inlineStr">
-        <is>
-          <t>7 150 ₽/т — ниже порога 9 000 ₽/т; NaCl ≥96,5%, помол №3</t>
-        </is>
-      </c>
-      <c r="U13" s="13" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Спецодежда</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>32616438570</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>открыть</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>ООО «ТЭК-2»</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>Московская обл.</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>223-ФЗ</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>14.10 08:00</t>
-        </is>
-      </c>
-      <c r="I14" s="11" t="n">
-        <v>4810414</v>
-      </c>
-      <c r="J14" s="11" t="n">
-        <v>3583552</v>
-      </c>
-      <c r="K14" s="12" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="L14" s="11" t="n"/>
-      <c r="M14" s="12" t="n"/>
-      <c r="N14" s="11" t="n">
-        <v>376049</v>
-      </c>
-      <c r="O14" s="12" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="P14" s="8" t="inlineStr">
-        <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="Q14" s="8" t="inlineStr">
-        <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="R14" s="8" t="inlineStr">
-        <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="S14" s="8" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>Зимняя спецодежда + костюмы от дуги и сварщика; подача завтра утром</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="18" t="inlineStr"/>
-      <c r="B15" s="18" t="inlineStr"/>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr"/>
+      <c r="B9" s="18" t="inlineStr"/>
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr"/>
-      <c r="E15" s="18" t="inlineStr"/>
-      <c r="F15" s="18" t="inlineStr"/>
-      <c r="G15" s="18" t="inlineStr"/>
-      <c r="H15" s="18" t="inlineStr"/>
-      <c r="I15" s="19" t="n">
-        <v>50789448</v>
-      </c>
-      <c r="J15" s="19" t="n">
-        <v>27210959</v>
-      </c>
-      <c r="K15" s="18" t="n"/>
-      <c r="L15" s="18" t="n"/>
-      <c r="M15" s="18" t="n"/>
-      <c r="N15" s="19" t="n">
-        <v>12577358</v>
-      </c>
-      <c r="O15" s="18" t="n"/>
-      <c r="P15" s="18" t="n"/>
-      <c r="Q15" s="18" t="n"/>
-      <c r="R15" s="18" t="n"/>
-      <c r="S15" s="18" t="n"/>
-      <c r="T15" s="18" t="n"/>
-      <c r="U15" s="18" t="n"/>
+      <c r="D9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr"/>
+      <c r="F9" s="18" t="inlineStr"/>
+      <c r="G9" s="18" t="inlineStr"/>
+      <c r="H9" s="18" t="inlineStr"/>
+      <c r="I9" s="19" t="n">
+        <v>24282047</v>
+      </c>
+      <c r="J9" s="19" t="n">
+        <v>10667771</v>
+      </c>
+      <c r="K9" s="18" t="n"/>
+      <c r="L9" s="18" t="n"/>
+      <c r="M9" s="18" t="n"/>
+      <c r="N9" s="19" t="n">
+        <v>7954583</v>
+      </c>
+      <c r="O9" s="18" t="n"/>
+      <c r="P9" s="18" t="n"/>
+      <c r="Q9" s="18" t="n"/>
+      <c r="R9" s="18" t="n"/>
+      <c r="S9" s="18" t="n"/>
+      <c r="T9" s="18" t="n"/>
+      <c r="U9" s="18" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:U14"/>
+  <autoFilter ref="A3:U8"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/TOP_PROFIT_3_15_1210.xlsx
+++ b/TOP_PROFIT_3_15_1210.xlsx
@@ -94,59 +94,80 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -510,7 +531,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -538,606 +559,646 @@
     <col width="11" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Топ лотов по прибыли: НМЦК 3–15 млн ₽, подача с 16.10.2026, без жёстких условий — ВНУТРЕННЯЯ</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
+      <c r="T1" s="2" t="n"/>
+      <c r="U1" s="2" t="n"/>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Исключены: обеспечение исполнения ≥30% (Ульяновск), требование опыта (Самара), закупки у ед. поставщика, лицензии, лоты &gt;15 млн, лоты с истёкшим сроком, лоты без расчёта прибыли (Дубна). УСН 15%, прибыль чистая.</t>
         </is>
       </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
+      <c r="T2" s="2" t="n"/>
+      <c r="U2" s="2" t="n"/>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3" ht="51" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Категория</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>№ закупки</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Ссылка</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Заказчик</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Регион</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Закон / способ</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Подача (МСК)</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>НМЦК, ₽</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Себестоимость, ₽</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Маржа</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>Прибыль при НМЦК, ₽</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>Ожид. снижение</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>Прибыль при ожид. снижении, ₽</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>Безубыток до снижения</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>Обеспечение заявки</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>Обеспечение исполнения</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>Аванс</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>Только СМП</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t>Что важно / проверить</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="U3" s="3" t="inlineStr">
         <is>
           <t>Достоверность</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Соль</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>32616451106</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>ООО «Департамент городского хозяйства»</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Московская обл.</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>223-ФЗ, иной способ (не аукцион)</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>16.10 10:00</t>
         </is>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I4" s="8" t="n">
         <v>6724000</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="J4" s="8" t="n">
         <v>1800000</v>
       </c>
-      <c r="K4" s="7" t="n">
+      <c r="K4" s="9" t="n">
         <v>0.73</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="L4" s="8" t="n">
         <v>4089375</v>
       </c>
-      <c r="M4" s="7" t="n">
+      <c r="M4" s="9" t="n">
         <v>0.15</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="N4" s="8" t="n">
         <v>3238924</v>
       </c>
-      <c r="O4" s="7" t="n">
+      <c r="O4" s="9" t="n">
         <v>0.72</v>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="P4" s="5" t="inlineStr">
         <is>
           <t>1% (67 240 ₽)</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>10% (672 400 ₽)</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="R4" s="5" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="S4" s="5" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="T4" s="5" t="inlineStr">
         <is>
           <t>Соль 400 т × 16 810 ₽/т; себест. 4 500 ₽/т с доставкой</t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr">
+      <c r="U4" s="5" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="8" t="n">
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Спецодежда</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>32616431081</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>ФБУ «Госуда…» (Госрезерв/ФБУ)</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>223-ФЗ, иной способ (не аукцион)</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="H5" s="11" t="inlineStr">
         <is>
           <t>19.10 08:00</t>
         </is>
       </c>
-      <c r="I5" s="11" t="n">
+      <c r="I5" s="14" t="n">
         <v>3637476</v>
       </c>
-      <c r="J5" s="11" t="n">
+      <c r="J5" s="14" t="n">
         <v>1276759</v>
       </c>
-      <c r="K5" s="12" t="n">
+      <c r="K5" s="15" t="n">
         <v>0.64</v>
       </c>
-      <c r="L5" s="11" t="n"/>
-      <c r="M5" s="12" t="n"/>
-      <c r="N5" s="11" t="n">
+      <c r="L5" s="14" t="n"/>
+      <c r="M5" s="15" t="n"/>
+      <c r="N5" s="14" t="n">
         <v>1605856</v>
       </c>
-      <c r="O5" s="12" t="n">
+      <c r="O5" s="15" t="n">
         <v>0.62</v>
       </c>
-      <c r="P5" s="8" t="inlineStr">
+      <c r="P5" s="11" t="inlineStr">
         <is>
           <t>не указано</t>
         </is>
       </c>
-      <c r="Q5" s="8" t="inlineStr">
+      <c r="Q5" s="11" t="inlineStr">
         <is>
           <t>не указано</t>
         </is>
       </c>
-      <c r="R5" s="8" t="inlineStr">
+      <c r="R5" s="11" t="inlineStr">
         <is>
           <t>не указано</t>
         </is>
       </c>
-      <c r="S5" s="8" t="inlineStr">
+      <c r="S5" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="T5" s="8" t="inlineStr">
+      <c r="T5" s="11" t="inlineStr">
         <is>
           <t>18 позиций; цен за ед. в ЕИС нет — маржа = НМЦК против нашей себестоимости по каталогу Тракт; НМЦК в 2,8 раза выше каталога — проверить ТЗ (ткани, ГОСТ, логотипы)</t>
         </is>
       </c>
-      <c r="U5" s="8" t="inlineStr">
+      <c r="U5" s="11" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Соль</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>0851300006226000106</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>МКУ г. Новосибирска «Дзержинка»</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Новосибирская обл.</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>44-ФЗ, аукцион (цена за ед.)</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>16.10 05:00</t>
         </is>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="8" t="n">
         <v>4400000</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="J6" s="8" t="n">
         <v>1800000</v>
       </c>
-      <c r="K6" s="7" t="n">
+      <c r="K6" s="9" t="n">
         <v>0.59</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="L6" s="8" t="n">
         <v>2129779</v>
       </c>
-      <c r="M6" s="7" t="n">
+      <c r="M6" s="9" t="n">
         <v>0.15</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="N6" s="8" t="n">
         <v>1573267</v>
       </c>
-      <c r="O6" s="7" t="n">
+      <c r="O6" s="9" t="n">
         <v>0.57</v>
       </c>
-      <c r="P6" s="3" t="inlineStr">
+      <c r="P6" s="5" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="Q6" s="3" t="inlineStr">
+      <c r="Q6" s="5" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="R6" s="3" t="inlineStr">
+      <c r="R6" s="5" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="S6" s="3" t="inlineStr">
+      <c r="S6" s="5" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="T6" s="3" t="inlineStr">
+      <c r="T6" s="5" t="inlineStr">
         <is>
           <t>~400 т × 11 000 ₽/т, МКР; объём не определён</t>
         </is>
       </c>
-      <c r="U6" s="3" t="inlineStr">
+      <c r="U6" s="5" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="8" t="n">
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Форменная одежда</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>0358200022926000030</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>ГКУ РО «Ростовская обл. поисково-спасательная служба»</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>Ростовская обл.</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>44-ФЗ, аукцион</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="H7" s="11" t="inlineStr">
         <is>
           <t>19.10 09:00</t>
         </is>
       </c>
-      <c r="I7" s="11" t="n">
+      <c r="I7" s="14" t="n">
         <v>6224421</v>
       </c>
-      <c r="J7" s="11" t="n">
+      <c r="J7" s="14" t="n">
         <v>3716512</v>
       </c>
-      <c r="K7" s="12" t="n">
+      <c r="K7" s="15" t="n">
         <v>0.39</v>
       </c>
-      <c r="L7" s="11" t="n"/>
-      <c r="M7" s="12" t="n"/>
-      <c r="N7" s="11" t="n">
+      <c r="L7" s="14" t="n"/>
+      <c r="M7" s="15" t="n"/>
+      <c r="N7" s="14" t="n">
         <v>995417</v>
       </c>
-      <c r="O7" s="12" t="n">
+      <c r="O7" s="15" t="n">
         <v>0.36</v>
       </c>
-      <c r="P7" s="8" t="inlineStr">
+      <c r="P7" s="11" t="inlineStr">
         <is>
           <t>1% (62 244 ₽)</t>
         </is>
       </c>
-      <c r="Q7" s="8" t="inlineStr">
+      <c r="Q7" s="11" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="R7" s="8" t="inlineStr">
+      <c r="R7" s="11" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="S7" s="8" t="inlineStr">
+      <c r="S7" s="11" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="T7" s="8" t="inlineStr">
+      <c r="T7" s="11" t="inlineStr">
         <is>
           <t>Пошив с символикой ПСС РО (шевроны, кокетки); только РФ; комбинезоны посчитаны как комплекты</t>
         </is>
       </c>
-      <c r="U7" s="8" t="inlineStr">
+      <c r="U7" s="11" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="13" t="n">
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Соль</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>0131300000626001316</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>МБУ «Комбинат благоустройства Ленинского р-на», Воронеж</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>Воронежская обл.</t>
         </is>
       </c>
-      <c r="G8" s="13" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>44-ФЗ, аукцион</t>
         </is>
       </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t>16.10 09:00</t>
         </is>
       </c>
-      <c r="I8" s="16" t="n">
+      <c r="I8" s="20" t="n">
         <v>3296150</v>
       </c>
-      <c r="J8" s="16" t="n">
+      <c r="J8" s="20" t="n">
         <v>2074500</v>
       </c>
-      <c r="K8" s="17" t="n">
+      <c r="K8" s="21" t="n">
         <v>0.37</v>
       </c>
-      <c r="L8" s="16" t="n">
+      <c r="L8" s="20" t="n">
         <v>958016</v>
       </c>
-      <c r="M8" s="17" t="n">
+      <c r="M8" s="21" t="n">
         <v>0.15</v>
       </c>
-      <c r="N8" s="16" t="n">
+      <c r="N8" s="20" t="n">
         <v>541119</v>
       </c>
-      <c r="O8" s="17" t="n">
+      <c r="O8" s="21" t="n">
         <v>0.35</v>
       </c>
-      <c r="P8" s="13" t="inlineStr">
+      <c r="P8" s="17" t="inlineStr">
         <is>
           <t>1% (32 962 ₽)</t>
         </is>
       </c>
-      <c r="Q8" s="13" t="inlineStr">
+      <c r="Q8" s="17" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="R8" s="13" t="inlineStr">
+      <c r="R8" s="17" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="S8" s="13" t="inlineStr">
+      <c r="S8" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="T8" s="13" t="inlineStr">
+      <c r="T8" s="17" t="inlineStr">
         <is>
           <t>7 150 ₽/т — ниже порога 9 000 ₽/т; NaCl ≥96,5%, помол №3</t>
         </is>
       </c>
-      <c r="U8" s="13" t="inlineStr">
+      <c r="U8" s="17" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="18" t="inlineStr"/>
-      <c r="B9" s="18" t="inlineStr"/>
-      <c r="C9" s="18" t="inlineStr">
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="22" t="inlineStr"/>
+      <c r="B9" s="22" t="inlineStr"/>
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr"/>
-      <c r="E9" s="18" t="inlineStr"/>
-      <c r="F9" s="18" t="inlineStr"/>
-      <c r="G9" s="18" t="inlineStr"/>
-      <c r="H9" s="18" t="inlineStr"/>
-      <c r="I9" s="19" t="n">
+      <c r="D9" s="22" t="inlineStr"/>
+      <c r="E9" s="22" t="inlineStr"/>
+      <c r="F9" s="22" t="inlineStr"/>
+      <c r="G9" s="22" t="inlineStr"/>
+      <c r="H9" s="22" t="inlineStr"/>
+      <c r="I9" s="23" t="n">
         <v>24282047</v>
       </c>
-      <c r="J9" s="19" t="n">
+      <c r="J9" s="23" t="n">
         <v>10667771</v>
       </c>
-      <c r="K9" s="18" t="n"/>
-      <c r="L9" s="18" t="n"/>
-      <c r="M9" s="18" t="n"/>
-      <c r="N9" s="19" t="n">
+      <c r="K9" s="24" t="n"/>
+      <c r="L9" s="24" t="n"/>
+      <c r="M9" s="24" t="n"/>
+      <c r="N9" s="23" t="n">
         <v>7954583</v>
       </c>
-      <c r="O9" s="18" t="n"/>
-      <c r="P9" s="18" t="n"/>
-      <c r="Q9" s="18" t="n"/>
-      <c r="R9" s="18" t="n"/>
-      <c r="S9" s="18" t="n"/>
-      <c r="T9" s="18" t="n"/>
-      <c r="U9" s="18" t="n"/>
+      <c r="O9" s="24" t="n"/>
+      <c r="P9" s="24" t="n"/>
+      <c r="Q9" s="24" t="n"/>
+      <c r="R9" s="24" t="n"/>
+      <c r="S9" s="24" t="n"/>
+      <c r="T9" s="24" t="n"/>
+      <c r="U9" s="24" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:U8"/>
@@ -1149,5 +1210,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>